--- a/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
+++ b/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
@@ -1,43 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="证券池调整历史" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证券池调整历史" sheetId="1" r:id="R9bb42e8c85f142a2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="楷体"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="楷体"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -61,36 +57,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="42"/>
+        <patternFill>
           <bgColor indexed="42"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="22"/>
+        <patternFill>
           <bgColor indexed="22"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -326,7 +319,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -335,13 +328,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -375,17 +368,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -440,262 +422,287 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="22" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="22" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>调整人</t>
+          <t xml:space="preserve">调整人</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>提交日期</t>
+          <t xml:space="preserve">提交日期</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>证券简称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>证券代码</t>
-        </is>
+          <t xml:space="preserve">证券简称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v>ISIN</v>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>证券类型</t>
+          <t xml:space="preserve">证券类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发行主体名称</t>
+          <t xml:space="preserve">发行主体名称</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>调整类型</t>
+          <t xml:space="preserve">调整类型</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>调整方向</t>
+          <t xml:space="preserve">调整方向</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>调整原因</t>
+          <t xml:space="preserve">调整原因</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>投资池名称</t>
+          <t xml:space="preserve">投资池名称</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>审核状态</t>
+          <t xml:space="preserve">审核状态</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>是否ABS</t>
+          <t xml:space="preserve">是否ABS</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>是否担保</t>
+          <t xml:space="preserve">是否担保</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>是否永续</t>
+          <t xml:space="preserve">是否永续</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>是否次级</t>
+          <t xml:space="preserve">是否次级</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>是否私募</t>
+          <t xml:space="preserve">是否私募</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>是否含权</t>
-        </is>
+          <t xml:space="preserve">是否含权</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="str">
+        <v>沪市代码</v>
+      </c>
+      <c r="S1" s="1" t="str">
+        <v>深市代码</v>
+      </c>
+      <c r="T1" s="1" t="str">
+        <v>银行间代码</v>
+      </c>
+      <c r="U1" s="1" t="str">
+        <v>北交所代码</v>
+      </c>
+      <c r="V1" s="1" t="str">
+        <v>其他市场代码</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>{data.adjusterName}</t>
+          <t xml:space="preserve">{data.adjusterName}</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>{data.submitTime}</t>
+          <t xml:space="preserve">{data.submitTime}</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityShortName}</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>{data.securityCode}</t>
-        </is>
+          <t xml:space="preserve">{data.securityShortName}</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>{data.isinCode}</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityTypeName}</t>
+          <t xml:space="preserve">{data.securityTypeName}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{data.issuer}</t>
+          <t xml:space="preserve">{data.issuer}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{data.adjustType}</t>
+          <t xml:space="preserve">{data.adjustType}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>{data.adjustMode}</t>
+          <t xml:space="preserve">{data.adjustMode}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>{data.adjustReason}</t>
+          <t xml:space="preserve">{data.adjustReason}</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>{data.targetPoolPath}</t>
+          <t xml:space="preserve">{data.targetPoolPath}</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>{data.auditStatusLabel}</t>
+          <t xml:space="preserve">{data.auditStatusLabel}</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>{data.absLabel}</t>
+          <t xml:space="preserve">{data.absLabel}</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>{data.guarantLabel}</t>
+          <t xml:space="preserve">{data.guarantLabel}</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>{data.yxLabel}</t>
+          <t xml:space="preserve">{data.yxLabel}</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>{data.cjLabel}</t>
+          <t xml:space="preserve">{data.cjLabel}</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>{data.privateLabel}</t>
+          <t xml:space="preserve">{data.privateLabel}</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>{data.inrightLabel}</t>
-        </is>
+          <t xml:space="preserve">{data.inrightLabel}</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="str">
+        <v>{data.windCodeSh}</v>
+      </c>
+      <c r="S2" s="2" t="str">
+        <v>{data.windCodeSz}</v>
+      </c>
+      <c r="T2" s="2" t="str">
+        <v>{data.windCodeNib}</v>
+      </c>
+      <c r="U2" s="2" t="str">
+        <v>{data.windCodeBj}</v>
+      </c>
+      <c r="V2" s="2" t="str">
+        <v>{data.windCodeNbc}</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L1048576">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M1048576">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N1048576">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O1048576">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P1048576">
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q1048576">
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
+++ b/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
@@ -1,39 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证券池调整历史" sheetId="1" r:id="R9bb42e8c85f142a2"/>
+    <sheet name="证券池调整历史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="楷体"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="楷体"/>
     </font>
     <font>
+      <name val="楷体"/>
       <sz val="11"/>
-      <name val="楷体"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,33 +61,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="42"/>
           <bgColor indexed="42"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor indexed="22"/>
           <bgColor indexed="22"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -319,7 +326,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -328,13 +335,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -368,6 +375,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -422,287 +440,262 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V2"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="22" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="22" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="22" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="22" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="22" hidden="0" customWidth="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整人</t>
+          <t>调整人</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">提交日期</t>
+          <t>提交日期</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券简称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>ISIN</v>
+          <t>证券简称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>证券代码</t>
+        </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券类型</t>
+          <t>证券类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">发行主体名称</t>
+          <t>发行主体名称</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整类型</t>
+          <t>调整类型</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整方向</t>
+          <t>调整方向</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整原因</t>
+          <t>调整原因</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">投资池名称</t>
+          <t>投资池名称</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">审核状态</t>
+          <t>审核状态</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否ABS</t>
+          <t>是否ABS</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否担保</t>
+          <t>是否担保</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否永续</t>
+          <t>是否永续</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否次级</t>
+          <t>是否次级</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否私募</t>
+          <t>是否私募</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否含权</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="str">
-        <v>沪市代码</v>
-      </c>
-      <c r="S1" s="1" t="str">
-        <v>深市代码</v>
-      </c>
-      <c r="T1" s="1" t="str">
-        <v>银行间代码</v>
-      </c>
-      <c r="U1" s="1" t="str">
-        <v>北交所代码</v>
-      </c>
-      <c r="V1" s="1" t="str">
-        <v>其他市场代码</v>
+          <t>是否含权</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.adjusterName}</t>
+          <t>{data.adjusterName}</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.submitTime}</t>
+          <t>{data.submitTime}</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityShortName}</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="str">
-        <v>{data.isinCode}</v>
+          <t>{data.securityShortName}</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>{data.securityCode}</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityTypeName}</t>
+          <t>{data.securityTypeName}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.issuer}</t>
+          <t>{data.issuer}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.adjustType}</t>
+          <t>{data.adjustType}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.adjustMode}</t>
+          <t>{data.adjustMode}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.adjustReason}</t>
+          <t>{data.adjustReason}</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.targetPoolPath}</t>
+          <t>{data.targetPoolPath}</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.auditStatusLabel}</t>
+          <t>{data.auditStatusLabel}</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.absLabel}</t>
+          <t>{data.absLabel}</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.guarantLabel}</t>
+          <t>{data.guarantLabel}</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.yxLabel}</t>
+          <t>{data.yxLabel}</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.cjLabel}</t>
+          <t>{data.cjLabel}</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.privateLabel}</t>
+          <t>{data.privateLabel}</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.inrightLabel}</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="str">
-        <v>{data.windCodeSh}</v>
-      </c>
-      <c r="S2" s="2" t="str">
-        <v>{data.windCodeSz}</v>
-      </c>
-      <c r="T2" s="2" t="str">
-        <v>{data.windCodeNib}</v>
-      </c>
-      <c r="U2" s="2" t="str">
-        <v>{data.windCodeBj}</v>
-      </c>
-      <c r="V2" s="2" t="str">
-        <v>{data.windCodeNbc}</v>
+          <t>{data.inrightLabel}</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N1048576">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O1048576">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P1048576">
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q1048576">
-    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"是"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
+++ b/src/main/resources/xlsx/security_pool_adjust_history_export_template.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,7 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -559,6 +560,9 @@
           <t>是否含权</t>
         </is>
       </c>
+      <c r="R1" s="1" t="str">
+        <v>是否标准信用债</v>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -645,6 +649,9 @@
         <is>
           <t>{data.inrightLabel}</t>
         </is>
+      </c>
+      <c r="R2" s="2" t="str">
+        <v>{data.stdCreditLabel}</v>
       </c>
     </row>
   </sheetData>
@@ -696,6 +703,14 @@
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R1048576">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
+      <formula>"是"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="1">
+      <formula>"否"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>